--- a/data/b2_bonsucesso/B2 Bonsucesso 03-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 03-2026.xlsx
@@ -4864,25 +4864,25 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>502.15</v>
+        <v>507.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1378.7</v>
+        <v>3096.18</v>
       </c>
     </row>
     <row r="4">
@@ -4900,115 +4900,115 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>66343.03</v>
+        <v>64821.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46089</v>
+        <v>46086</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3921.65</v>
+        <v>1407.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46091</v>
+        <v>46087</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3600</v>
+        <v>1610.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46093</v>
+        <v>46089</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2536.77</v>
+        <v>3891.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1248.09</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46096</v>
+        <v>46093</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>10763.4</v>
+        <v>1485.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46096</v>
+        <v>46094</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1731.41</v>
+        <v>1595.85</v>
       </c>
     </row>
     <row r="11">
@@ -5017,106 +5017,106 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>4107.6</v>
+        <v>10757.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46098</v>
+        <v>46096</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3818.02</v>
+        <v>2630.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46098</v>
+        <v>46096</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>2122.55</v>
+        <v>4130.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1252.09</v>
+        <v>23313.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46101</v>
+        <v>46103</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>22461.82</v>
+        <v>3784.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46103</v>
+        <v>46104</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3999.99</v>
+        <v>1590.54</v>
       </c>
     </row>
     <row r="17">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>4028.53</v>
+        <v>4057.98</v>
       </c>
     </row>
     <row r="18">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1210.45</v>
+        <v>1131.48</v>
       </c>
     </row>
   </sheetData>
